--- a/fiji/FINAL_PANEL.xlsx
+++ b/fiji/FINAL_PANEL.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V70" t="inlineStr"/>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V71" t="inlineStr"/>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V72" t="inlineStr"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V73" t="inlineStr"/>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="V74" t="inlineStr"/>
@@ -17440,7 +17440,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -17518,7 +17518,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -17908,7 +17908,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -18064,7 +18064,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -18220,7 +18220,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -18298,7 +18298,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -18376,7 +18376,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -18454,7 +18454,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -18922,7 +18922,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -19156,7 +19156,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -19588,7 +19588,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -19798,7 +19798,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -20098,7 +20098,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -20410,7 +20410,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -20488,7 +20488,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -20566,7 +20566,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -20800,7 +20800,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -20878,7 +20878,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -20956,7 +20956,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -21100,7 +21100,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -21466,7 +21466,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -21544,7 +21544,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -21622,7 +21622,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -21778,7 +21778,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -22012,7 +22012,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -22090,7 +22090,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -22168,7 +22168,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -22246,7 +22246,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -22324,7 +22324,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -22402,7 +22402,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -22554,7 +22554,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -22788,7 +22788,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P72" t="inlineStr"/>
@@ -22862,7 +22862,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -22936,7 +22936,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -23170,7 +23170,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -23248,7 +23248,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -23326,7 +23326,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -23482,7 +23482,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -23560,7 +23560,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -23872,7 +23872,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -23950,7 +23950,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -24028,7 +24028,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -24106,7 +24106,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P89" t="inlineStr"/>
@@ -24180,7 +24180,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P91" t="inlineStr"/>
@@ -24320,7 +24320,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -24452,7 +24452,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -24842,7 +24842,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -24920,7 +24920,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -24998,7 +24998,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -25076,7 +25076,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -25154,7 +25154,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -25220,7 +25220,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -25286,7 +25286,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -25352,7 +25352,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -25430,7 +25430,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -25586,7 +25586,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -25664,7 +25664,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -25820,7 +25820,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -25898,7 +25898,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -25976,7 +25976,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -26132,7 +26132,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -26210,7 +26210,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P117" t="inlineStr"/>
@@ -26284,7 +26284,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -26362,7 +26362,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -26440,7 +26440,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -26518,7 +26518,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -26752,7 +26752,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -26830,7 +26830,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -26908,7 +26908,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -26986,7 +26986,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P127" t="inlineStr"/>
@@ -27060,7 +27060,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -27138,7 +27138,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -27216,7 +27216,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -27372,7 +27372,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -27528,7 +27528,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -27606,7 +27606,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -27684,7 +27684,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -27840,7 +27840,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P138" t="inlineStr"/>
@@ -27914,7 +27914,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -27992,7 +27992,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -28070,7 +28070,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -28226,7 +28226,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -28382,7 +28382,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -28456,7 +28456,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -28690,7 +28690,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -28768,7 +28768,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -28846,7 +28846,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -29002,7 +29002,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -29080,7 +29080,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -29236,7 +29236,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -29314,7 +29314,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -29392,7 +29392,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -29470,7 +29470,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -29548,7 +29548,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -29626,7 +29626,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P161" t="inlineStr"/>
@@ -29700,7 +29700,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P162" t="inlineStr"/>
@@ -29774,7 +29774,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -29852,7 +29852,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -29930,7 +29930,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -30008,7 +30008,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P167" t="inlineStr"/>
@@ -30160,7 +30160,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -30238,7 +30238,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -30316,7 +30316,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -30472,7 +30472,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -30550,7 +30550,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -30628,7 +30628,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P174" t="inlineStr"/>
@@ -30702,7 +30702,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -30780,7 +30780,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P178" t="inlineStr"/>
@@ -31006,7 +31006,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P179" t="inlineStr"/>
@@ -31080,7 +31080,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -31158,7 +31158,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -31314,7 +31314,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -31392,7 +31392,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -31470,7 +31470,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -31548,7 +31548,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -31626,7 +31626,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -31692,7 +31692,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -31758,7 +31758,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -31820,7 +31820,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -31898,7 +31898,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -31976,7 +31976,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P192" t="inlineStr"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P193" t="inlineStr"/>
@@ -32124,7 +32124,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -32202,7 +32202,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P195" t="inlineStr"/>
@@ -32276,7 +32276,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P196" t="inlineStr"/>
@@ -32350,7 +32350,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P197" t="inlineStr"/>
@@ -32424,7 +32424,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P199" t="inlineStr"/>
@@ -32564,7 +32564,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -32630,7 +32630,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -32852,7 +32852,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -32930,7 +32930,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -33004,7 +33004,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P206" t="inlineStr"/>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P207" t="inlineStr"/>
@@ -33144,7 +33144,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P208" t="inlineStr"/>
@@ -33202,7 +33202,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P209" t="inlineStr"/>
@@ -33260,7 +33260,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P210" t="inlineStr"/>
@@ -33318,7 +33318,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P211" t="inlineStr"/>
@@ -33388,7 +33388,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P212" t="inlineStr"/>
@@ -33458,7 +33458,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P213" t="inlineStr"/>
@@ -33528,7 +33528,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P214" t="inlineStr"/>
@@ -33598,7 +33598,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P215" t="inlineStr"/>
@@ -33668,7 +33668,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P216" t="inlineStr"/>
@@ -33738,7 +33738,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P217" t="inlineStr"/>
@@ -33796,7 +33796,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P218" t="inlineStr"/>
@@ -33854,7 +33854,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P219" t="inlineStr"/>
@@ -33912,7 +33912,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="P220" t="inlineStr"/>
@@ -45504,7 +45504,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
     </row>
@@ -45543,7 +45543,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
     </row>
@@ -45582,7 +45582,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
     </row>
@@ -45621,7 +45621,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
     </row>
@@ -45660,7 +45660,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
     </row>
@@ -45699,7 +45699,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
     </row>
@@ -45738,7 +45738,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
     </row>
@@ -45777,7 +45777,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
     </row>
@@ -45816,7 +45816,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
     </row>
@@ -45855,7 +45855,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
     </row>
@@ -48753,7 +48753,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -48828,7 +48828,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -48903,7 +48903,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -48978,7 +48978,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -49053,7 +49053,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -49128,7 +49128,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -49203,7 +49203,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -49278,7 +49278,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -49353,7 +49353,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -49428,7 +49428,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -49503,7 +49503,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -49578,7 +49578,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -49653,7 +49653,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -49728,7 +49728,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -49803,7 +49803,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -49878,7 +49878,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -49953,7 +49953,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -50028,7 +50028,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -50103,7 +50103,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -50178,7 +50178,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -50253,7 +50253,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -50328,7 +50328,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -50403,7 +50403,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -50478,7 +50478,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -50553,7 +50553,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -50628,7 +50628,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -50698,7 +50698,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -50773,7 +50773,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -50848,7 +50848,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -50923,7 +50923,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -50998,7 +50998,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -51073,7 +51073,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -51143,7 +51143,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -51218,7 +51218,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -51293,7 +51293,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -51368,7 +51368,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -51438,7 +51438,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -51513,7 +51513,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -51588,7 +51588,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -51663,7 +51663,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -51738,7 +51738,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -51813,7 +51813,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -51888,7 +51888,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -51963,7 +51963,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -52038,7 +52038,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -52113,7 +52113,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -52183,7 +52183,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -52258,7 +52258,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -52333,7 +52333,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -52408,7 +52408,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -52483,7 +52483,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -52558,7 +52558,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -52633,7 +52633,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -52708,7 +52708,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -52783,7 +52783,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -52858,7 +52858,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -52928,7 +52928,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -52998,7 +52998,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -53068,7 +53068,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -53143,7 +53143,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -53218,7 +53218,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -53293,7 +53293,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -53368,7 +53368,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -53443,7 +53443,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -53518,7 +53518,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -53593,7 +53593,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -53668,7 +53668,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -53743,7 +53743,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -53818,7 +53818,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -53893,7 +53893,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -53968,7 +53968,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -54043,7 +54043,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -54118,7 +54118,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -54193,7 +54193,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -54268,7 +54268,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -54343,7 +54343,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -54418,7 +54418,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -54493,7 +54493,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -54568,7 +54568,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -54643,7 +54643,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -54718,7 +54718,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -54793,7 +54793,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -54868,7 +54868,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -54943,7 +54943,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -55013,7 +55013,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -55088,7 +55088,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -55163,7 +55163,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -55238,7 +55238,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -55313,7 +55313,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -55388,7 +55388,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -55463,7 +55463,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -55538,7 +55538,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -55613,7 +55613,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -55683,7 +55683,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -55758,7 +55758,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -55833,7 +55833,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -55908,7 +55908,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -55983,7 +55983,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -56058,7 +56058,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -56133,7 +56133,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -56208,7 +56208,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -56283,7 +56283,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -56358,7 +56358,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -56433,7 +56433,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -56508,7 +56508,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -56578,7 +56578,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -56653,7 +56653,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -56728,7 +56728,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -56803,7 +56803,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -56878,7 +56878,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -56953,7 +56953,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -57028,7 +57028,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -57103,7 +57103,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -57178,7 +57178,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -57253,7 +57253,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -57323,7 +57323,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -57393,7 +57393,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -57468,7 +57468,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -57538,7 +57538,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -57613,7 +57613,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -57688,7 +57688,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -57763,7 +57763,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -57838,7 +57838,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -57913,7 +57913,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -57988,7 +57988,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -58063,7 +58063,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -58138,7 +58138,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -58213,7 +58213,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -58288,7 +58288,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -58363,7 +58363,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -58438,7 +58438,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -58513,7 +58513,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -58588,7 +58588,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -58663,7 +58663,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -58738,7 +58738,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -58813,7 +58813,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -58888,7 +58888,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -58963,7 +58963,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -59038,7 +59038,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -59113,7 +59113,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -59188,7 +59188,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -59263,7 +59263,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -59338,7 +59338,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -59413,7 +59413,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -59483,7 +59483,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -59558,7 +59558,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -59633,7 +59633,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -59708,7 +59708,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -59783,7 +59783,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -59858,7 +59858,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -59928,7 +59928,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -60003,7 +60003,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -60078,7 +60078,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -60153,7 +60153,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -60223,7 +60223,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -60298,7 +60298,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -60373,7 +60373,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -60448,7 +60448,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -60523,7 +60523,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -60598,7 +60598,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -60673,7 +60673,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -60748,7 +60748,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -60823,7 +60823,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -60898,7 +60898,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -60973,7 +60973,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -61043,7 +61043,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -61118,7 +61118,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -61193,7 +61193,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -61268,7 +61268,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -61343,7 +61343,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -61418,7 +61418,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -61493,7 +61493,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -61568,7 +61568,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -61643,7 +61643,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -61713,7 +61713,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -61783,7 +61783,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -61858,7 +61858,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -61928,7 +61928,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -62003,7 +62003,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -62078,7 +62078,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -62153,7 +62153,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -62228,7 +62228,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -62303,7 +62303,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -62378,7 +62378,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -62489,7 +62489,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -62537,7 +62537,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -62585,7 +62585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -62633,7 +62633,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -62681,7 +62681,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -62729,7 +62729,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -62777,7 +62777,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -62825,7 +62825,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -62873,7 +62873,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -62921,7 +62921,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -62969,7 +62969,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -63017,7 +63017,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -63065,7 +63065,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -63113,7 +63113,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -63161,7 +63161,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -63209,7 +63209,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -63257,7 +63257,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -63305,7 +63305,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -63353,7 +63353,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -63401,7 +63401,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -63449,7 +63449,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -63497,7 +63497,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -63545,7 +63545,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -63593,7 +63593,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -63641,7 +63641,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -63689,7 +63689,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -63737,7 +63737,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -63785,7 +63785,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -63833,7 +63833,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -63881,7 +63881,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -63929,7 +63929,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -63977,7 +63977,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -64025,7 +64025,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -64073,7 +64073,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -64121,7 +64121,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -64169,7 +64169,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -64217,7 +64217,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -64265,7 +64265,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -64313,7 +64313,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -64361,7 +64361,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -64409,7 +64409,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -64457,7 +64457,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -64505,7 +64505,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -64553,7 +64553,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -64601,7 +64601,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -64649,7 +64649,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -64697,7 +64697,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -64745,7 +64745,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -64793,7 +64793,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -64841,7 +64841,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -64889,7 +64889,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -64937,7 +64937,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -64985,7 +64985,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -65033,7 +65033,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -65081,7 +65081,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -65129,7 +65129,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -65177,7 +65177,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -65225,7 +65225,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -65273,7 +65273,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -65321,7 +65321,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -65369,7 +65369,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -65417,7 +65417,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -65465,7 +65465,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -65513,7 +65513,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -65561,7 +65561,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -65609,7 +65609,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -65657,7 +65657,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -65705,7 +65705,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -65753,7 +65753,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -65801,7 +65801,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -65849,7 +65849,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -65897,7 +65897,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -65945,7 +65945,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -65993,7 +65993,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -66041,7 +66041,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -66089,7 +66089,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H77" t="n">
@@ -66137,7 +66137,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -66185,7 +66185,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -66233,7 +66233,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -66281,7 +66281,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -66329,7 +66329,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -66377,7 +66377,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -66425,7 +66425,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -66473,7 +66473,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -66521,7 +66521,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -66569,7 +66569,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -66617,7 +66617,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -66665,7 +66665,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -66713,7 +66713,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -66761,7 +66761,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -66809,7 +66809,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -66857,7 +66857,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -66905,7 +66905,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -66953,7 +66953,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -67001,7 +67001,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -67049,7 +67049,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -67097,7 +67097,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H98" t="n">
@@ -67145,7 +67145,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -67193,7 +67193,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -67241,7 +67241,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -67289,7 +67289,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H102" t="n">
@@ -67337,7 +67337,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -67385,7 +67385,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -67433,7 +67433,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -67481,7 +67481,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -67529,7 +67529,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H107" t="n">
@@ -67577,7 +67577,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -67625,7 +67625,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H109" t="n">
@@ -67673,7 +67673,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -67721,7 +67721,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -67769,7 +67769,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H112" t="n">
@@ -67817,7 +67817,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -67865,7 +67865,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -67913,7 +67913,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -67961,7 +67961,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -68009,7 +68009,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -68057,7 +68057,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -68105,7 +68105,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -68153,7 +68153,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -68201,7 +68201,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -68249,7 +68249,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H122" t="n">
@@ -68297,7 +68297,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -68345,7 +68345,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -68393,7 +68393,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H125" t="n">
@@ -68441,7 +68441,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H126" t="n">
@@ -68489,7 +68489,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H127" t="n">
@@ -68537,7 +68537,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H128" t="n">
@@ -68585,7 +68585,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -68633,7 +68633,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -68681,7 +68681,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -68729,7 +68729,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -68777,7 +68777,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -68825,7 +68825,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -68873,7 +68873,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -68921,7 +68921,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -68969,7 +68969,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -69017,7 +69017,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -69065,7 +69065,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -69113,7 +69113,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H140" t="n">
@@ -69161,7 +69161,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -69209,7 +69209,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H142" t="n">
@@ -69257,7 +69257,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H143" t="n">
@@ -69305,7 +69305,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H144" t="n">
@@ -69353,7 +69353,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H145" t="n">
@@ -69401,7 +69401,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H146" t="n">
@@ -69449,7 +69449,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H147" t="n">
@@ -69497,7 +69497,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H148" t="n">
@@ -69545,7 +69545,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H149" t="n">
@@ -69593,7 +69593,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H150" t="n">
@@ -69641,7 +69641,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H151" t="n">
@@ -69689,7 +69689,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H152" t="n">
@@ -69737,7 +69737,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H153" t="n">
@@ -69785,7 +69785,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H154" t="n">
@@ -69833,7 +69833,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H155" t="n">
@@ -69881,7 +69881,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H156" t="n">
@@ -69929,7 +69929,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H157" t="n">
@@ -69977,7 +69977,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H158" t="n">
@@ -70025,7 +70025,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H159" t="n">
@@ -70073,7 +70073,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H160" t="n">
@@ -70121,7 +70121,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H161" t="n">
@@ -70169,7 +70169,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H162" t="n">
@@ -70217,7 +70217,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H163" t="n">
@@ -70265,7 +70265,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H164" t="n">
@@ -70313,7 +70313,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H165" t="n">
@@ -70361,7 +70361,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H166" t="n">
@@ -70409,7 +70409,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H167" t="n">
@@ -70457,7 +70457,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H168" t="n">
@@ -70505,7 +70505,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H169" t="n">
@@ -70553,7 +70553,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H170" t="n">
@@ -70601,7 +70601,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="H171" t="n">

--- a/fiji/FINAL_PANEL.xlsx
+++ b/fiji/FINAL_PANEL.xlsx
@@ -17443,11 +17443,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Roads, Bridges and Jetties</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17521,11 +17517,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Roads, Bridges and Jetties</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17599,11 +17591,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Roads, Bridges and Jetties</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17677,11 +17665,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Utility Services</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17755,11 +17739,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Utility Services</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17833,11 +17813,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Utility Services</t>
-        </is>
-      </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17911,11 +17887,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Primary Education</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17989,11 +17961,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Primary Education</t>
-        </is>
-      </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18067,11 +18035,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Primary Education</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18145,11 +18109,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Secondary Education</t>
-        </is>
-      </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18223,11 +18183,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Secondary Education</t>
-        </is>
-      </c>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18301,11 +18257,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Secondary Education</t>
-        </is>
-      </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18379,11 +18331,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Fiji Police</t>
-        </is>
-      </c>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18457,11 +18405,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Fiji Police</t>
-        </is>
-      </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18535,11 +18479,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Fiji Police</t>
-        </is>
-      </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18613,11 +18553,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Health Services</t>
-        </is>
-      </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18691,11 +18627,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Health Services</t>
-        </is>
-      </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18769,11 +18701,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Divisional Health Services; Health Services</t>
-        </is>
-      </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18847,11 +18775,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Social Welfare</t>
-        </is>
-      </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -18925,11 +18849,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Social Welfare</t>
-        </is>
-      </c>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -19003,11 +18923,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Social Welfare</t>
-        </is>
-      </c>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -19081,11 +18997,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Tertiary Technical Education</t>
-        </is>
-      </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19159,11 +19071,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Higher Education Institutions</t>
-        </is>
-      </c>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -19237,11 +19145,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Higher Education Institutions</t>
-        </is>
-      </c>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -19303,11 +19207,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Peacekeeping - RFMF</t>
-        </is>
-      </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -19369,11 +19269,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Peacekeeping - RFMF</t>
-        </is>
-      </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -19435,11 +19331,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Peacekeeping - RFMF</t>
-        </is>
-      </c>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -19513,11 +19405,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Sugar Development</t>
-        </is>
-      </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -19591,11 +19479,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Sugar Development</t>
-        </is>
-      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19669,11 +19553,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Sugar Development</t>
-        </is>
-      </c>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -19735,11 +19615,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Medical Supplies and Equipment</t>
-        </is>
-      </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -19801,11 +19677,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Medical Supplies and Equipment</t>
-        </is>
-      </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -19867,11 +19739,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Medical Supplies and Equipment</t>
-        </is>
-      </c>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -19945,11 +19813,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -20023,11 +19887,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -20101,11 +19961,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -20179,11 +20035,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Department of Tourism</t>
-        </is>
-      </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -20257,11 +20109,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Department of Tourism</t>
-        </is>
-      </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -20335,11 +20183,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Department of Tourism</t>
-        </is>
-      </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -20413,11 +20257,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Policy and Administration</t>
-        </is>
-      </c>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -20491,11 +20331,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Policy and Administration</t>
-        </is>
-      </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -20569,11 +20405,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Policy and Administration</t>
-        </is>
-      </c>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -20647,11 +20479,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Department of Communication</t>
-        </is>
-      </c>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -20725,11 +20553,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Department of Communication</t>
-        </is>
-      </c>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -20803,11 +20627,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Department of Communication</t>
-        </is>
-      </c>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -20881,11 +20701,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Civil Service</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -20959,11 +20775,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Civil Service</t>
-        </is>
-      </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -21037,11 +20849,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Civil Service</t>
-        </is>
-      </c>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -21103,11 +20911,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Fiji Corrections Service</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -21169,11 +20973,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Fiji Corrections Service</t>
-        </is>
-      </c>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -21235,11 +21035,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Fiji Corrections Service</t>
-        </is>
-      </c>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -21313,11 +21109,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Economic and Trade Unit</t>
-        </is>
-      </c>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -21391,11 +21183,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Economic and Trade Unit</t>
-        </is>
-      </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -21469,11 +21257,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Economic and Trade Unit</t>
-        </is>
-      </c>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -21547,11 +21331,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Economic and Trade Unit</t>
-        </is>
-      </c>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -21625,11 +21405,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Economic and Trade Unit</t>
-        </is>
-      </c>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -21703,11 +21479,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Economic and Trade Unit</t>
-        </is>
-      </c>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -21781,11 +21553,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Crops</t>
-        </is>
-      </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -21859,11 +21627,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Crops</t>
-        </is>
-      </c>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -21937,11 +21701,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Crops</t>
-        </is>
-      </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -22015,11 +21775,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Foreign Missions</t>
-        </is>
-      </c>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -22093,11 +21849,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Foreign Missions</t>
-        </is>
-      </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -22171,11 +21923,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Foreign Missions</t>
-        </is>
-      </c>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -22249,11 +21997,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Housing</t>
-        </is>
-      </c>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -22327,11 +22071,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Housing</t>
-        </is>
-      </c>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -22405,11 +22145,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Housing</t>
-        </is>
-      </c>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -22557,11 +22293,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Public Enterprises Reform</t>
-        </is>
-      </c>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -22635,11 +22367,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Public Enterprises</t>
-        </is>
-      </c>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -22713,11 +22441,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Peacekeeping - RFMF</t>
-        </is>
-      </c>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -22939,11 +22663,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Policy and Administration</t>
-        </is>
-      </c>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -23017,11 +22737,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Policy and Administration</t>
-        </is>
-      </c>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -23095,11 +22811,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Policy and Administration</t>
-        </is>
-      </c>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -23173,11 +22885,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Land Management</t>
-        </is>
-      </c>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -23251,11 +22959,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Land Management</t>
-        </is>
-      </c>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -23329,11 +23033,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Land Management</t>
-        </is>
-      </c>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -23407,11 +23107,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Land Management</t>
-        </is>
-      </c>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -23485,11 +23181,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Land Management</t>
-        </is>
-      </c>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -23563,11 +23255,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Land Management</t>
-        </is>
-      </c>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -23641,11 +23329,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Economic and Trade Unit</t>
-        </is>
-      </c>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -23719,11 +23403,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Department of Co-operative Business</t>
-        </is>
-      </c>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -23797,11 +23477,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Micro, Small and Medium Enterprises Central Coordinating Agency</t>
-        </is>
-      </c>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -23875,11 +23551,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Fisheries</t>
-        </is>
-      </c>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -23953,11 +23625,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Fisheries</t>
-        </is>
-      </c>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -24031,11 +23699,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Fisheries</t>
-        </is>
-      </c>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -24183,11 +23847,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Economic and Trade Unit</t>
-        </is>
-      </c>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -24323,11 +23983,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Prime Minister's Office</t>
-        </is>
-      </c>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -24389,11 +24045,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Prime Minister's Office</t>
-        </is>
-      </c>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -24455,11 +24107,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Prime Minister's Office</t>
-        </is>
-      </c>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -24533,11 +24181,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -24611,11 +24255,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -24689,11 +24329,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -24767,11 +24403,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Forestry</t>
-        </is>
-      </c>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -24845,11 +24477,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Forestry</t>
-        </is>
-      </c>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -24923,11 +24551,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Forestry</t>
-        </is>
-      </c>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -25001,11 +24625,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Tertiary Technical Education</t>
-        </is>
-      </c>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -25079,11 +24699,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Tertiary Technical Education</t>
-        </is>
-      </c>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -25157,11 +24773,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>Tertiary Technical Education</t>
-        </is>
-      </c>
+      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -25223,11 +24835,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>iTaukei Affairs</t>
-        </is>
-      </c>
+      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -25289,11 +24897,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>iTaukei Affairs</t>
-        </is>
-      </c>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -25355,11 +24959,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>iTaukei Affairs</t>
-        </is>
-      </c>
+      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -25433,11 +25033,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Disaster Management; Meteorological Services</t>
-        </is>
-      </c>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -25511,11 +25107,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Meteorological Services</t>
-        </is>
-      </c>
+      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -25589,11 +25181,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Disaster Management; Meteorological Services</t>
-        </is>
-      </c>
+      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -25667,11 +25255,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Attorney - General's Chambers</t>
-        </is>
-      </c>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -25745,11 +25329,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Attorney - General's Chambers</t>
-        </is>
-      </c>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -25823,11 +25403,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Attorney - General's Chambers</t>
-        </is>
-      </c>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -25901,11 +25477,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Fiji Bureau of Statistics</t>
-        </is>
-      </c>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -25979,11 +25551,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>Fiji Bureau of Statistics</t>
-        </is>
-      </c>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -26057,11 +25625,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>Fiji Bureau of Statistics</t>
-        </is>
-      </c>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -26135,11 +25699,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Technical and Support Services</t>
-        </is>
-      </c>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -26287,11 +25847,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>Technical and Support Services</t>
-        </is>
-      </c>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -26365,11 +25921,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
+      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -26443,11 +25995,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
+      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -26521,11 +26069,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
+      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -26599,11 +26143,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>Mineral Resources</t>
-        </is>
-      </c>
+      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -26677,11 +26217,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>Mineral Resources</t>
-        </is>
-      </c>
+      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -26755,11 +26291,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>Mineral Resources</t>
-        </is>
-      </c>
+      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -26833,11 +26365,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>Public Enterprises Reform</t>
-        </is>
-      </c>
+      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -26911,11 +26439,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>Public Enterprises Reform</t>
-        </is>
-      </c>
+      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -27063,11 +26587,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>Rural Development Services</t>
-        </is>
-      </c>
+      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -27141,11 +26661,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>Rural Development Services</t>
-        </is>
-      </c>
+      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -27219,11 +26735,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>Rural Development Services</t>
-        </is>
-      </c>
+      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -27297,11 +26809,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>Curriculum Development</t>
-        </is>
-      </c>
+      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -27375,11 +26883,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>Curriculum Development</t>
-        </is>
-      </c>
+      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -27453,11 +26957,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>Curriculum Development</t>
-        </is>
-      </c>
+      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -27531,11 +27031,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>Justice</t>
-        </is>
-      </c>
+      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -27609,11 +27105,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>Justice</t>
-        </is>
-      </c>
+      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -27687,11 +27179,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>Justice</t>
-        </is>
-      </c>
+      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -27765,11 +27253,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>Land Drainage and Flood Protection</t>
-        </is>
-      </c>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -27917,11 +27401,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>Waterways Services</t>
-        </is>
-      </c>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -27995,11 +27475,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>Youth</t>
-        </is>
-      </c>
+      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -28073,11 +27549,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>Youth</t>
-        </is>
-      </c>
+      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -28151,11 +27623,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>Youth</t>
-        </is>
-      </c>
+      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -28229,11 +27697,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>Other Services</t>
-        </is>
-      </c>
+      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -28307,11 +27771,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>Water and Sewerage</t>
-        </is>
-      </c>
+      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -28459,11 +27919,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>Town and Country Planning</t>
-        </is>
-      </c>
+      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -28537,11 +27993,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>Town and Country Planning</t>
-        </is>
-      </c>
+      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -28615,11 +28067,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Town and Country Planning</t>
-        </is>
-      </c>
+      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -28693,11 +28141,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>Heritage and Arts</t>
-        </is>
-      </c>
+      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -28771,11 +28215,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>Heritage and Arts</t>
-        </is>
-      </c>
+      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -28849,11 +28289,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>Heritage and Arts</t>
-        </is>
-      </c>
+      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -28927,11 +28363,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>Women and Gender Development</t>
-        </is>
-      </c>
+      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -29005,11 +28437,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>Women and Gender Development</t>
-        </is>
-      </c>
+      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -29083,11 +28511,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>Women and Gender Development</t>
-        </is>
-      </c>
+      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -29161,11 +28585,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>Disaster Management</t>
-        </is>
-      </c>
+      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -29239,11 +28659,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P156" t="inlineStr">
-        <is>
-          <t>Disaster Management</t>
-        </is>
-      </c>
+      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -29317,11 +28733,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>Disaster Management</t>
-        </is>
-      </c>
+      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -29395,11 +28807,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P158" t="inlineStr">
-        <is>
-          <t>Information</t>
-        </is>
-      </c>
+      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -29473,11 +28881,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>Information</t>
-        </is>
-      </c>
+      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -29551,11 +28955,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>Information</t>
-        </is>
-      </c>
+      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -29777,11 +29177,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P163" t="inlineStr">
-        <is>
-          <t>Common Services</t>
-        </is>
-      </c>
+      <c r="P163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -29855,11 +29251,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P164" t="inlineStr">
-        <is>
-          <t>Rural Infrastructure</t>
-        </is>
-      </c>
+      <c r="P164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -29933,11 +29325,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P165" t="inlineStr">
-        <is>
-          <t>Rural Infrastructure</t>
-        </is>
-      </c>
+      <c r="P165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -30011,11 +29399,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>Rural Infrastructure</t>
-        </is>
-      </c>
+      <c r="P166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -30163,11 +29547,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>Department of Immigration</t>
-        </is>
-      </c>
+      <c r="P168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -30241,11 +29621,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>Department of Immigration</t>
-        </is>
-      </c>
+      <c r="P169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -30319,11 +29695,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>Department of National Trade Measurement and Standard</t>
-        </is>
-      </c>
+      <c r="P170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -30397,11 +29769,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>Department of National Trade Measurement and Standard</t>
-        </is>
-      </c>
+      <c r="P171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -30475,11 +29843,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>Department of National Trade Measurement and Standard</t>
-        </is>
-      </c>
+      <c r="P172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -30553,11 +29917,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>Policy and Administration</t>
-        </is>
-      </c>
+      <c r="P173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -30705,11 +30065,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>Policy and Administration</t>
-        </is>
-      </c>
+      <c r="P175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -30857,11 +30213,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>Department of Civil Aviation</t>
-        </is>
-      </c>
+      <c r="P177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -31083,11 +30435,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P180" t="inlineStr">
-        <is>
-          <t>Land Resource Planning</t>
-        </is>
-      </c>
+      <c r="P180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -31161,11 +30509,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P181" t="inlineStr">
-        <is>
-          <t>Land Resource Planning</t>
-        </is>
-      </c>
+      <c r="P181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -31239,11 +30583,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P182" t="inlineStr">
-        <is>
-          <t>Water and Sewerage</t>
-        </is>
-      </c>
+      <c r="P182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -31317,11 +30657,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>Water and Sewerage</t>
-        </is>
-      </c>
+      <c r="P183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -31395,11 +30731,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P184" t="inlineStr">
-        <is>
-          <t>Water and Sewerage</t>
-        </is>
-      </c>
+      <c r="P184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -31473,11 +30805,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P185" t="inlineStr">
-        <is>
-          <t>Research, Development and Training</t>
-        </is>
-      </c>
+      <c r="P185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -31551,11 +30879,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P186" t="inlineStr">
-        <is>
-          <t>Research, Development and Training</t>
-        </is>
-      </c>
+      <c r="P186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -31629,11 +30953,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P187" t="inlineStr">
-        <is>
-          <t>Research, Development and Training</t>
-        </is>
-      </c>
+      <c r="P187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -31695,11 +31015,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P188" t="inlineStr">
-        <is>
-          <t>Department of Co-operative Business</t>
-        </is>
-      </c>
+      <c r="P188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -31823,11 +31139,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P190" t="inlineStr">
-        <is>
-          <t>Department of Co-operative Business</t>
-        </is>
-      </c>
+      <c r="P190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -31901,11 +31213,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>Rehabilitation and Rural Housing</t>
-        </is>
-      </c>
+      <c r="P191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -32127,11 +31435,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>Peacekeeping - Police</t>
-        </is>
-      </c>
+      <c r="P194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -32427,11 +31731,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>Policy and Administration</t>
-        </is>
-      </c>
+      <c r="P198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -32567,11 +31867,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>Cabinet Office</t>
-        </is>
-      </c>
+      <c r="P200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -32633,11 +31929,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P201" t="inlineStr">
-        <is>
-          <t>Cabinet Office</t>
-        </is>
-      </c>
+      <c r="P201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -32699,11 +31991,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P202" t="inlineStr">
-        <is>
-          <t>Cabinet Office</t>
-        </is>
-      </c>
+      <c r="P202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -32777,11 +32065,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P203" t="inlineStr">
-        <is>
-          <t>Asset Monitoring Unit</t>
-        </is>
-      </c>
+      <c r="P203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -32855,11 +32139,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>Asset Monitoring Unit</t>
-        </is>
-      </c>
+      <c r="P204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -32933,11 +32213,7 @@
           <t>FJD thousand</t>
         </is>
       </c>
-      <c r="P205" t="inlineStr">
-        <is>
-          <t>Asset Monitoring Unit</t>
-        </is>
-      </c>
+      <c r="P205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
